--- a/output/感染症対策指針_いいかいご.xlsx
+++ b/output/感染症対策指針_いいかいご.xlsx
@@ -806,7 +806,7 @@
     <row r="64" ht="48" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>感染対策委員会は、おおむね6か月に1回以上（4月・10月を予定）定期的に開催する。また、感染症発生時には、必要に応じて随時開催する。開催はテレビ電話装置等を活用して行うことができる。</t>
+          <t>感染対策委員会は、おおむね6か月に1回以上（6月・11月を予定）定期的に開催する。また、感染症発生時には、必要に応じて随時開催する。開催はテレビ電話装置等を活用して行うことができる。</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="B82" s="12" t="inlineStr">
         <is>
-          <t>5月・11月</t>
+          <t>6月・11月</t>
         </is>
       </c>
       <c r="C82" s="13" t="n"/>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t>5月</t>
+          <t>6月</t>
         </is>
       </c>
       <c r="C92" s="13" t="n"/>
